--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
+        <v>856</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>632</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>467</v>
-      </c>
       <c r="D7" s="10" t="n">
-        <v>635</v>
+        <v>817</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1018,7 +1018,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1037,42 +1037,42 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H17" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I17" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L17" s="12" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,47 +1253,47 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L19" s="12" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,42 +1307,42 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J20" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K20" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1361,47 +1361,47 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K21" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>05589</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>ZOLA PREDOSA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,47 +1415,47 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>05512</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>CASTEL SAN PIETRO TERME</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1469,35 +1469,35 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1526,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>234</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.03846153846153846</v>
+        <v>9</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>237</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.008438818565400843</v>
+        <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>214</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.3551401869158878</v>
+        <v>76</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>138</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.01449275362318841</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>86</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.2674418604651163</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>65</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.03076923076923077</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>78</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.2307692307692308</v>
+        <v>18</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>75</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.02666666666666667</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>57</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.01754385964912281</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>42</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.02380952380952381</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>856</v>
+        <v>907</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>632</v>
+        <v>675</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>817</v>
+        <v>861</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>12</v>
@@ -1004,7 +1004,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>12</v>
@@ -1112,14 +1112,14 @@
         <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
@@ -1274,7 +1274,7 @@
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>6</v>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,19 +1415,19 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>6</v>
@@ -1436,14 +1436,14 @@
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>907</v>
+        <v>952</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>675</v>
+        <v>715</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>861</v>
+        <v>900</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>405</v>
+        <v>424</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>2</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>12</v>
@@ -1004,7 +1004,7 @@
         <v>34</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,22 +1037,22 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F15" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>51</v>
-      </c>
       <c r="J15" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>14</v>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>34</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>12</v>
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>19</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
@@ -1271,10 +1271,10 @@
         <v>2</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1382,14 +1382,14 @@
         <v>4</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1436,14 +1436,14 @@
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>952</v>
+        <v>1055</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>715</v>
+        <v>810</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>900</v>
+        <v>936</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IMOLA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>246</v>
+        <v>30</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>182</v>
+        <v>56</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>IMOLA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -929,42 +929,42 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>25</v>
+        <v>246</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -983,42 +983,42 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>59</v>
@@ -1154,7 +1154,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>41</v>
@@ -1163,10 +1163,10 @@
         <v>14</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>19</v>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
@@ -1211,23 +1211,23 @@
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
@@ -1274,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>8</v>
@@ -1328,7 +1328,7 @@
         <v>9</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>2</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
@@ -1373,23 +1373,23 @@
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1055</v>
+        <v>1132</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>810</v>
+        <v>864</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>936</v>
+        <v>979</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>2</v>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G16" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H16" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>30</v>
@@ -1157,23 +1157,23 @@
         <v>33</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1256,28 +1256,28 @@
         <v>36</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J19" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
         <v>11</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N24" headerRowCount="1">
-  <autoFilter ref="A10:N24"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O24" headerRowCount="1">
+  <autoFilter ref="A10:O24"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA M.E.LEPIDO 206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>388</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>362</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>466</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>323</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA NUOVA BAZZANESE 8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>138</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>138</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA SELICE KM. 2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>275</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA FERRARESE 166</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIALE DELL'INDUSTRIA 44</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA SHAKESPEARE SNC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>VIA STALINGRADO 59/4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA G. DOZZA, 33</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="M18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>COMPLANARE S. LAZZARO SNC</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>26</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L19" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA MASSARENTI, 221/3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA RISORGIMENTO 77</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K22" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="N22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA EMILIA PONENTE 210</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,29 +1595,31 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>VIALE D AGOSTINO 141</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="12" t="n">
         <v>0</v>
       </c>
@@ -1549,7 +1632,10 @@
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1132</v>
+        <v>1180</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>864</v>
+        <v>899</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H12" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="J12" s="12" t="n">
+      <c r="M12" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>266</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>103</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>45</v>
@@ -1155,13 +1155,13 @@
         <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>14</v>
@@ -1217,14 +1217,14 @@
         <v>11</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>20</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,52 +1255,52 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COMPLANARE S. LAZZARO SNC</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1180</v>
+        <v>1236</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>899</v>
+        <v>939</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1008</v>
+        <v>1045</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1022,13 +1022,13 @@
         <v>106</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>84</v>
@@ -1040,10 +1040,10 @@
         <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>16</v>
@@ -1099,7 +1099,7 @@
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>40</v>
@@ -1149,23 +1149,23 @@
         <v>8</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>30</v>
@@ -1214,10 +1214,10 @@
         <v>14</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>20</v>
@@ -1255,13 +1255,13 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
@@ -1273,17 +1273,17 @@
         <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>2</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1236</v>
+        <v>1272</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>939</v>
+        <v>963</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1045</v>
+        <v>1084</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>93</v>
@@ -978,10 +978,10 @@
         <v>52</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>8</v>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G14" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="H14" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="K14" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1140,13 +1140,13 @@
         <v>77</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>47</v>
@@ -1158,21 +1158,21 @@
         <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,42 +1196,42 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>28</v>
@@ -1391,13 +1391,13 @@
         <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1435,13 +1435,13 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1512,14 +1512,14 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1272</v>
+        <v>1304</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>963</v>
+        <v>983</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1084</v>
+        <v>1098</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>40</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         <v>130</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>93</v>
@@ -981,7 +981,7 @@
         <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>8</v>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>86</v>
@@ -1037,13 +1037,13 @@
         <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>99</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>2</v>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>43</v>
@@ -1273,10 +1273,10 @@
         <v>14</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>20</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
@@ -1335,14 +1335,14 @@
         <v>7</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
         <v>10</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>4</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1512,14 +1512,14 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1304</v>
+        <v>1381</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>983</v>
+        <v>1033</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1098</v>
+        <v>1148</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>462</v>
+        <v>496</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>381</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>194</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>93</v>
@@ -978,17 +978,17 @@
         <v>52</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,16 +1137,16 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>48</v>
@@ -1155,17 +1155,17 @@
         <v>13</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M18" s="12" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>29</v>
@@ -1391,10 +1391,10 @@
         <v>10</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>4</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1381</v>
+        <v>1443</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1033</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1148</v>
+        <v>1202</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>550</v>
+        <v>581</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>42</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1022,13 +1022,13 @@
         <v>117</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>94</v>
@@ -1040,10 +1040,10 @@
         <v>23</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1081,13 +1081,13 @@
         <v>115</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>102</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>63</v>
@@ -1099,7 +1099,7 @@
         <v>54</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>3</v>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>23</v>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>4</v>
@@ -1435,13 +1435,13 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>0</v>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1443</v>
+        <v>1485</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1075</v>
+        <v>1105</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1202</v>
+        <v>1248</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>41</v>
@@ -1040,7 +1040,7 @@
         <v>23</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>43</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>19</v>
@@ -1099,10 +1099,10 @@
         <v>54</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
@@ -1172,7 +1172,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,42 +1196,42 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K17" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L17" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,35 +1255,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>4</v>
@@ -1435,7 +1435,7 @@
         <v>37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>1</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>6</v>
@@ -1512,14 +1512,14 @@
         <v>0</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O24" headerRowCount="1">
-  <autoFilter ref="A10:O24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O27" headerRowCount="1">
+  <autoFilter ref="A10:O27"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1485</v>
+        <v>1654</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1105</v>
+        <v>1244</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1248</v>
+        <v>1330</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>55420</t>
+          <t>05543</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BOLOGNA</t>
+          <t>SASSO MARCONI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA SHAKESPEARE SNC</t>
+          <t>VIA KENNEDY 7</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,42 +1137,42 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA SHAKESPEARE SNC</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1196,42 +1196,42 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,42 +1255,42 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N18" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN LAZZARO DI SAVENA</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COMPLANARE S. LAZZARO SNC</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>55422</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO 36</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,52 +1432,52 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05589</t>
+          <t>25565</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ZOLA PREDOSA</t>
+          <t>SAN LAZZARO DI SAVENA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA RISORGIMENTO 77</t>
+          <t>COMPLANARE S. LAZZARO SNC</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1491,52 +1491,52 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05512</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CASTEL SAN PIETRO TERME</t>
+          <t>BOLOGNA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA PONENTE 210</t>
+          <t>VIA CRISTOFORO COLOMBO 36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,57 +1585,234 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>05589</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ZOLA PREDOSA</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VIA RISORGIMENTO 77</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>05512</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CASTEL SAN PIETRO TERME</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>VIA EMILIA PONENTE 210</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="N25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>15552</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>IMOLA</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>VIALE D AGOSTINO 141</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>MURGO LORENZO</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12" t="n">
+      <c r="F26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="n">
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="J26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>15572</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>MOLINELLA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>VIA PROVINCIALE SUPERIORE</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>MURGO LORENZO</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Tino Vincenzo - CR MURGO LORENZO.xlsx
@@ -684,13 +684,13 @@
         <v>17</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1654</v>
+        <v>1637</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1244</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1330</v>
+        <v>1302</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>246</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>219</v>
@@ -863,10 +863,10 @@
         <v>84</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>44</v>
@@ -913,7 +913,7 @@
         <v>130</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>60</v>
@@ -922,7 +922,7 @@
         <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>135</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>103</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>54</v>
@@ -995,7 +995,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>25556</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA FERRARESE 166</t>
+          <t>VIALE DELL'INDUSTRIA 44</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1019,42 +1019,42 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>78</v>
+        <v>257</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>127</v>
+        <v>258</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>54498</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 44</t>
+          <t>VIA FERRARESE 166</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>257</v>
+        <v>78</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>260</v>
+        <v>127</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>34</v>
@@ -1158,7 +1158,7 @@
         <v>20</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>2</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>73</v>
@@ -1208,7 +1208,7 @@
         <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>16</v>
@@ -1231,7 +1231,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>05588</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA STALINGRADO 59/4</t>
+          <t>VIA G. DOZZA, 33</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,42 +1255,42 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05588</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA G. DOZZA, 33</t>
+          <t>VIA STALINGRADO 59/4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,42 +1314,42 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N19" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L19" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05536</t>
+          <t>05530</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA ALDINI 186</t>
+          <t>VIA MASSARENTI, 221/3</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1376,39 +1376,39 @@
         <v>64</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05530</t>
+          <t>05536</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MASSARENTI, 221/3</t>
+          <t>VIA ALDINI 186</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>4</v>
@@ -1503,7 +1503,7 @@
         <v>67</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>11</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>1</v>
@@ -1562,7 +1562,7 @@
         <v>19</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>2</v>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>6</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>5</v>
